--- a/artfynd/A 21716-2025 artfynd.xlsx
+++ b/artfynd/A 21716-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -800,6 +800,493 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>128479230</v>
+      </c>
+      <c r="B3" t="n">
+        <v>98478</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Myrbjörkenskogen, Sura sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>555921</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6625029</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Litet bestånd</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Sören Larsson, Seppo Ormiskangas, Bengt Eriksson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>128479399</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57833</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Myrbjörkenskogen, Sura sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>555799</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6625105</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Sören Larsson, Seppo Ormiskangas, Bengt Eriksson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128479176</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91325</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Myrbjörken, Sura sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>555991</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6625095</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På granläga</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Sören Larsson, Seppo Ormiskangas, Bengt Eriksson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128479127</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57833</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Myrbjörkenskogen, Sura sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>556025</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6625101</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Sören Larsson, Seppo Ormiskangas, Bengt Eriksson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 21716-2025 artfynd.xlsx
+++ b/artfynd/A 21716-2025 artfynd.xlsx
@@ -806,7 +806,7 @@
         <v>128479230</v>
       </c>
       <c r="B3" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
         <v>128479399</v>
       </c>
       <c r="B4" t="n">
-        <v>57833</v>
+        <v>57845</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>128479176</v>
       </c>
       <c r="B5" t="n">
-        <v>91325</v>
+        <v>91417</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
         <v>128479127</v>
       </c>
       <c r="B6" t="n">
-        <v>57833</v>
+        <v>57845</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 21716-2025 artfynd.xlsx
+++ b/artfynd/A 21716-2025 artfynd.xlsx
@@ -806,7 +806,7 @@
         <v>128479230</v>
       </c>
       <c r="B3" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
         <v>128479399</v>
       </c>
       <c r="B4" t="n">
-        <v>57845</v>
+        <v>57849</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>128479176</v>
       </c>
       <c r="B5" t="n">
-        <v>91417</v>
+        <v>91423</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
         <v>128479127</v>
       </c>
       <c r="B6" t="n">
-        <v>57845</v>
+        <v>57849</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 21716-2025 artfynd.xlsx
+++ b/artfynd/A 21716-2025 artfynd.xlsx
@@ -806,7 +806,7 @@
         <v>128479230</v>
       </c>
       <c r="B3" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>128479176</v>
       </c>
       <c r="B5" t="n">
-        <v>91423</v>
+        <v>91429</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 21716-2025 artfynd.xlsx
+++ b/artfynd/A 21716-2025 artfynd.xlsx
@@ -806,7 +806,7 @@
         <v>128479230</v>
       </c>
       <c r="B3" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>128479176</v>
       </c>
       <c r="B5" t="n">
-        <v>91429</v>
+        <v>91431</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 21716-2025 artfynd.xlsx
+++ b/artfynd/A 21716-2025 artfynd.xlsx
@@ -806,7 +806,7 @@
         <v>128479230</v>
       </c>
       <c r="B3" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Sören Larsson, Seppo Ormiskangas, Bengt Eriksson</t>
+          <t>Bengt Eriksson, Seppo Ormiskangas, Sören Larsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 21716-2025 artfynd.xlsx
+++ b/artfynd/A 21716-2025 artfynd.xlsx
@@ -806,7 +806,7 @@
         <v>128479230</v>
       </c>
       <c r="B3" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bengt Eriksson, Seppo Ormiskangas, Sören Larsson</t>
+          <t>Sören Larsson, Seppo Ormiskangas, Bengt Eriksson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1054,7 +1054,7 @@
         <v>128479176</v>
       </c>
       <c r="B5" t="n">
-        <v>91431</v>
+        <v>91432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 21716-2025 artfynd.xlsx
+++ b/artfynd/A 21716-2025 artfynd.xlsx
@@ -806,7 +806,7 @@
         <v>128479230</v>
       </c>
       <c r="B3" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
         <v>128479399</v>
       </c>
       <c r="B4" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>128479176</v>
       </c>
       <c r="B5" t="n">
-        <v>91432</v>
+        <v>91459</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
         <v>128479127</v>
       </c>
       <c r="B6" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 21716-2025 artfynd.xlsx
+++ b/artfynd/A 21716-2025 artfynd.xlsx
@@ -806,7 +806,7 @@
         <v>128479230</v>
       </c>
       <c r="B3" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>128479176</v>
       </c>
       <c r="B5" t="n">
-        <v>91459</v>
+        <v>91464</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 21716-2025 artfynd.xlsx
+++ b/artfynd/A 21716-2025 artfynd.xlsx
@@ -1055,7 +1055,7 @@
         <v>128479399</v>
       </c>
       <c r="B5" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
         <v>128479127</v>
       </c>
       <c r="B6" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 21716-2025 artfynd.xlsx
+++ b/artfynd/A 21716-2025 artfynd.xlsx
@@ -1055,7 +1055,7 @@
         <v>128479399</v>
       </c>
       <c r="B5" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
         <v>128479127</v>
       </c>
       <c r="B6" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 21716-2025 artfynd.xlsx
+++ b/artfynd/A 21716-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,64 +675,55 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>70530644</v>
+        <v>128479176</v>
       </c>
       <c r="B2" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Myrbjörken, Sura sn, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>556115.9271259477</v>
+        <v>555991</v>
       </c>
       <c r="R2" t="n">
-        <v>6625128.565445064</v>
+        <v>6625095</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -756,27 +747,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2018-04-10</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2018-04-10</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Hackade i tall</t>
+          <t>På granläga</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,6 +776,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -796,39 +788,39 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Sören Larsson, Seppo Ormiskangas, Bengt Eriksson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128479230</v>
+        <v>70530644</v>
       </c>
       <c r="B3" t="n">
-        <v>98646</v>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -836,31 +828,26 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Myrbjörkenskogen, Sura sn, Vstm</t>
+          <t>Myrbjörken, Sura sn, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>555921</v>
+        <v>556116</v>
       </c>
       <c r="R3" t="n">
-        <v>6625029</v>
+        <v>6625129</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -884,27 +871,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2018-04-10</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2018-04-10</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Litet bestånd</t>
+          <t>Hackade i tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,7 +900,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -925,17 +911,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sören Larsson, Seppo Ormiskangas, Bengt Eriksson</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128479176</v>
+        <v>81992703</v>
       </c>
       <c r="B4" t="n">
-        <v>91480</v>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -943,30 +929,35 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -974,13 +965,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>555991</v>
+        <v>555743</v>
       </c>
       <c r="R4" t="n">
-        <v>6625095</v>
+        <v>6625193</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -989,7 +980,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>Surahammar</t>
+          <t>Skinnskatteberg</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -999,32 +990,27 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Sura</t>
+          <t>Gunnilbo</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2020-02-01</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2020-02-01</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På granläga</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1033,7 +1019,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1045,46 +1030,42 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Sören Larsson, Seppo Ormiskangas, Bengt Eriksson</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128479399</v>
+        <v>68475340</v>
       </c>
       <c r="B5" t="n">
-        <v>57887</v>
+        <v>58592</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>102125</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallbit</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pinicola enucleator</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
@@ -1092,20 +1073,19 @@
           <t>lockläte, övriga läten</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Myrbjörkenskogen, Sura sn, Vstm</t>
+          <t>Myrbjörken, Sura sn, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>555799</v>
+        <v>555743</v>
       </c>
       <c r="R5" t="n">
-        <v>6625105</v>
+        <v>6625193</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1114,7 +1094,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>Surahammar</t>
+          <t>Skinnskatteberg</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1124,27 +1104,32 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Sura</t>
+          <t>Gunnilbo</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2017-11-26</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2017-11-26</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>En flock hördes locka, kunde inte ses p.g.a. den höga skogen</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1164,17 +1149,21 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Sören Larsson, Seppo Ormiskangas, Bengt Eriksson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Sören Larsson, Greta Larsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Tätortsnära natur, Surahammars kommun</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128479127</v>
+        <v>68840092</v>
       </c>
       <c r="B6" t="n">
-        <v>57887</v>
+        <v>58114</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1201,30 +1190,29 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Myrbjörkenskogen, Sura sn, Vstm</t>
+          <t>Myrbjörken, Sura sn, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>556025</v>
+        <v>555743</v>
       </c>
       <c r="R6" t="n">
-        <v>6625101</v>
+        <v>6625193</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1233,7 +1221,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>Surahammar</t>
+          <t>Skinnskatteberg</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1243,27 +1231,32 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>Sura</t>
+          <t>Gunnilbo</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2018-01-01</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2018-01-01</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Fågelmatning</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1283,10 +1276,377 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128479127</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Myrbjörkenskogen, Sura sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>556025</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6625101</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
           <t>Sören Larsson, Seppo Ormiskangas, Bengt Eriksson</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr"/>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128479399</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Myrbjörkenskogen, Sura sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>555799</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6625105</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Sören Larsson, Seppo Ormiskangas, Bengt Eriksson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128479230</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Myrbjörkenskogen, Sura sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>555921</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6625029</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Litet bestånd</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Sören Larsson, Seppo Ormiskangas, Bengt Eriksson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 21716-2025 artfynd.xlsx
+++ b/artfynd/A 21716-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -792,6 +797,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128479176</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -915,6 +925,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70530644</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1034,6 +1049,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81992703</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1157,6 +1177,11 @@
           <t>Tätortsnära natur, Surahammars kommun</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68475340</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1280,6 +1305,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68840092</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1399,6 +1429,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128479127</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1518,6 +1553,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128479399</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1647,8 +1687,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128479230</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>